--- a/output/pdf_financials_xlsx/MTS.xlsx
+++ b/output/pdf_financials_xlsx/MTS.xlsx
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007085</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002847</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000332</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>5.6e-05</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1125,34 +1125,34 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.006484</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.064164</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.047323</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.038672</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.013288</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.027384</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.011215</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.012428</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.019327</v>
       </c>
     </row>
     <row r="13">
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.034121</v>
+        <v>-0.041206</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.415903</v>
+        <v>-0.41875</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.206147</v>
+        <v>-2.206267</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2152,34 +2152,34 @@
         <v>-0.6088980000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.406201</v>
+        <v>-0.406324</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.47329</v>
+        <v>-0.479774</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.803627</v>
+        <v>-1.867791</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.360401</v>
+        <v>-0.407724</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.561808</v>
+        <v>-0.60048</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.647746</v>
+        <v>-1.661034</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.221082</v>
+        <v>-2.248466</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.6608309999999999</v>
+        <v>-0.672046</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.041144</v>
+        <v>-1.053572</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-2.097799</v>
+        <v>-2.117126</v>
       </c>
     </row>
     <row r="28">
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.034121</v>
+        <v>-0.041206</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.415903</v>
+        <v>-0.41875</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.206147</v>
+        <v>-2.206267</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2278,34 +2278,34 @@
         <v>-0.608298</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.405785</v>
+        <v>-0.405908</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.47287</v>
+        <v>-0.479354</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.796055</v>
+        <v>-1.860219</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.340928</v>
+        <v>-0.388251</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.539108</v>
+        <v>-0.57778</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.62486</v>
+        <v>-1.638148</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.200046</v>
+        <v>-2.22743</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.641467</v>
+        <v>-0.652682</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.022512</v>
+        <v>-1.03494</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-2.080466</v>
+        <v>-2.099793</v>
       </c>
     </row>
     <row r="30">
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.242867</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.067458</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.281844</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.029241</v>
@@ -2596,13 +2596,13 @@
         <v>0.014601</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.061565</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.019683</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.021403</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.017302</v>
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.242867</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.067458</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.281844</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.029241</v>
@@ -2718,13 +2718,13 @@
         <v>0.074601</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0735</v>
+        <v>0.135065</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.153</v>
+        <v>0.172683</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.042</v>
+        <v>0.063403</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.083677</v>
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.242867</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.067458</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.416957</v>
+        <v>1.135113</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.43917</v>
@@ -3450,13 +3450,13 @@
         <v>0.413342</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.064856</v>
+        <v>0.003291</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.023015</v>
+        <v>0.003332</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.023327</v>
+        <v>0.001924</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.00151</v>
@@ -8171,22 +8171,22 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.041176</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.038363</v>
       </c>
     </row>
     <row r="125">
@@ -8232,22 +8232,22 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0405</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.041176</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.038363</v>
       </c>
     </row>
     <row r="126">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -24610,7 +24610,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -42232,7 +42236,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -49034,7 +49038,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -53076,7 +53080,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E427" s="5" t="n">

--- a/output/pdf_financials_xlsx/MTS.xlsx
+++ b/output/pdf_financials_xlsx/MTS.xlsx
@@ -794,13 +794,13 @@
         <v>1.377542</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.5801770000000001</v>
+        <v>0.616177</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.23307</v>
+        <v>0.25507</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.227123</v>
+        <v>0.229123</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.225154</v>
@@ -4651,49 +4651,49 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.318043</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="68">
@@ -7351,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004945</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005626</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -7372,19 +7372,19 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012398</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011582</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002165</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002408</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002314</v>
       </c>
     </row>
     <row r="112">
@@ -7531,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.509718</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.694255</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.043975</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.070907</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -8790,10 +8790,10 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004945</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005626</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8811,19 +8811,19 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012398</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011582</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002165</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002408</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8832,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002314</v>
       </c>
     </row>
     <row r="135">
@@ -8851,10 +8851,10 @@
         <v>-2.25303</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.72501</v>
+        <v>-0.729955</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.5348579999999999</v>
+        <v>-0.540484</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.548529</v>
@@ -8872,19 +8872,19 @@
         <v>-0.714901</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.678995</v>
+        <v>-0.691393</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.57489</v>
+        <v>-0.586472</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-0.856924</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.271592</v>
+        <v>-1.273757</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.966102</v>
+        <v>-1.96851</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-0.621518</v>
@@ -8893,7 +8893,7 @@
         <v>-0.885562</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-2.004916</v>
+        <v>-2.00723</v>
       </c>
     </row>
   </sheetData>
@@ -24124,7 +24124,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -24422,7 +24426,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -27784,7 +27792,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -28846,7 +28858,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -32534,7 +32550,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -35920,7 +35940,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -36986,7 +37010,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -39010,7 +39038,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -39116,7 +39148,11 @@
           <t>Proceeds from sales of marketable securities</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -46612,7 +46648,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -47560,7 +47600,11 @@
           <t>Director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -49678,7 +49722,11 @@
           <t>Director fees (Note 13)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
